--- a/Database/Table/Skill.xlsx
+++ b/Database/Table/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyProjects\Ju.GundamWars\Database\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A6B793-3B4C-4407-87CB-A64AB45EBF16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D5271A-A3FD-4F0A-A25F-35B59E43AF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12030" yWindow="0" windowWidth="16770" windowHeight="15600" activeTab="1" xr2:uid="{064ECAC2-0018-4D0D-8343-7CDBC6F8A70F}"/>
+    <workbookView xWindow="12030" yWindow="0" windowWidth="16770" windowHeight="15600" activeTab="2" xr2:uid="{064ECAC2-0018-4D0D-8343-7CDBC6F8A70F}"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="4" r:id="rId1"/>
@@ -11138,1450 +11138,1450 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C7AF441-215C-4472-BE50-4512DCBDC0EE}">
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="1">
+        <f>VLOOKUP(F2,Skill!C:E,3,FALSE)</f>
+        <v>8</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <f>VLOOKUP(C2,Skill!C:E,3,FALSE)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="1">
+        <f>VLOOKUP(F3,Skill!C:E,3,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1">
-        <f>VLOOKUP(C3,Skill!C:E,3,FALSE)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1">
+        <f>VLOOKUP(F4,Skill!C:E,3,FALSE)</f>
+        <v>22</v>
+      </c>
+      <c r="C4" s="6">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1">
-        <f>VLOOKUP(C4,Skill!C:E,3,FALSE)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="1">
+        <f>VLOOKUP(F5,Skill!C:E,3,FALSE)</f>
+        <v>23</v>
+      </c>
+      <c r="C5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1">
-        <f>VLOOKUP(C5,Skill!C:E,3,FALSE)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="1">
+        <f>VLOOKUP(F6,Skill!C:E,3,FALSE)</f>
+        <v>25</v>
+      </c>
+      <c r="C6" s="6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1">
-        <f>VLOOKUP(C6,Skill!C:E,3,FALSE)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="1">
+        <f>VLOOKUP(F7,Skill!C:E,3,FALSE)</f>
+        <v>24</v>
+      </c>
+      <c r="C7" s="6">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="6">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1">
-        <f>VLOOKUP(C7,Skill!C:E,3,FALSE)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="1">
+        <f>VLOOKUP(F8,Skill!C:E,3,FALSE)</f>
+        <v>28</v>
+      </c>
+      <c r="C8" s="6">
+        <v>7</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1">
-        <f>VLOOKUP(C8,Skill!C:E,3,FALSE)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="1">
+        <f>VLOOKUP(F9,Skill!C:E,3,FALSE)</f>
+        <v>33</v>
+      </c>
+      <c r="C9" s="6">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="6">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1">
-        <f>VLOOKUP(C9,Skill!C:E,3,FALSE)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="1">
+        <f>VLOOKUP(F10,Skill!C:E,3,FALSE)</f>
+        <v>34</v>
+      </c>
+      <c r="C10" s="6">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1">
-        <f>VLOOKUP(C10,Skill!C:E,3,FALSE)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="1">
+        <f>VLOOKUP(F11,Skill!C:E,3,FALSE)</f>
+        <v>37</v>
+      </c>
+      <c r="C11" s="6">
+        <v>10</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="6">
-        <v>10</v>
-      </c>
-      <c r="E11" s="1">
-        <f>VLOOKUP(C11,Skill!C:E,3,FALSE)</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="1">
+        <f>VLOOKUP(F12,Skill!C:E,3,FALSE)</f>
+        <v>38</v>
+      </c>
+      <c r="C12" s="6">
+        <v>11</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="6">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1">
-        <f>VLOOKUP(C12,Skill!C:E,3,FALSE)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="1">
+        <f>VLOOKUP(F13,Skill!C:E,3,FALSE)</f>
+        <v>46</v>
+      </c>
+      <c r="C13" s="6">
+        <v>12</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="6">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1">
-        <f>VLOOKUP(C13,Skill!C:E,3,FALSE)</f>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="1">
+        <f>VLOOKUP(F14,Skill!C:E,3,FALSE)</f>
+        <v>47</v>
+      </c>
+      <c r="C14" s="6">
+        <v>13</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="6">
-        <v>13</v>
-      </c>
-      <c r="E14" s="1">
-        <f>VLOOKUP(C14,Skill!C:E,3,FALSE)</f>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="1">
+        <f>VLOOKUP(F15,Skill!C:E,3,FALSE)</f>
+        <v>49</v>
+      </c>
+      <c r="C15" s="6">
+        <v>14</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="6">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1">
-        <f>VLOOKUP(C15,Skill!C:E,3,FALSE)</f>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="1">
+        <f>VLOOKUP(F16,Skill!C:E,3,FALSE)</f>
+        <v>50</v>
+      </c>
+      <c r="C16" s="6">
+        <v>15</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="6">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1">
-        <f>VLOOKUP(C16,Skill!C:E,3,FALSE)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="1">
+        <f>VLOOKUP(F17,Skill!C:E,3,FALSE)</f>
+        <v>51</v>
+      </c>
+      <c r="C17" s="6">
+        <v>16</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="6">
-        <v>16</v>
-      </c>
-      <c r="E17" s="1">
-        <f>VLOOKUP(C17,Skill!C:E,3,FALSE)</f>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="1">
+        <f>VLOOKUP(F18,Skill!C:E,3,FALSE)</f>
+        <v>54</v>
+      </c>
+      <c r="C18" s="6">
+        <v>17</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="F18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="6">
-        <v>17</v>
-      </c>
-      <c r="E18" s="1">
-        <f>VLOOKUP(C18,Skill!C:E,3,FALSE)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="1">
+        <f>VLOOKUP(F19,Skill!C:E,3,FALSE)</f>
+        <v>56</v>
+      </c>
+      <c r="C19" s="6">
+        <v>18</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="6">
-        <v>18</v>
-      </c>
-      <c r="E19" s="1">
-        <f>VLOOKUP(C19,Skill!C:E,3,FALSE)</f>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="1">
+        <f>VLOOKUP(F20,Skill!C:E,3,FALSE)</f>
+        <v>59</v>
+      </c>
+      <c r="C20" s="6">
+        <v>19</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="6">
-        <v>19</v>
-      </c>
-      <c r="E20" s="1">
-        <f>VLOOKUP(C20,Skill!C:E,3,FALSE)</f>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="1">
+        <f>VLOOKUP(F21,Skill!C:E,3,FALSE)</f>
+        <v>60</v>
+      </c>
+      <c r="C21" s="6">
+        <v>20</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="6">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1">
-        <f>VLOOKUP(C21,Skill!C:E,3,FALSE)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="1">
+        <f>VLOOKUP(F22,Skill!C:E,3,FALSE)</f>
+        <v>62</v>
+      </c>
+      <c r="C22" s="6">
+        <v>21</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="6">
-        <v>21</v>
-      </c>
-      <c r="E22" s="1">
-        <f>VLOOKUP(C22,Skill!C:E,3,FALSE)</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="1">
+        <f>VLOOKUP(F23,Skill!C:E,3,FALSE)</f>
+        <v>64</v>
+      </c>
+      <c r="C23" s="6">
+        <v>22</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="6">
-        <v>22</v>
-      </c>
-      <c r="E23" s="1">
-        <f>VLOOKUP(C23,Skill!C:E,3,FALSE)</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="1">
+        <f>VLOOKUP(F24,Skill!C:E,3,FALSE)</f>
+        <v>87</v>
+      </c>
+      <c r="C24" s="6">
+        <v>23</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="6">
-        <v>23</v>
-      </c>
-      <c r="E24" s="1">
-        <f>VLOOKUP(C24,Skill!C:E,3,FALSE)</f>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="1">
+        <f>VLOOKUP(F25,Skill!C:E,3,FALSE)</f>
+        <v>85</v>
+      </c>
+      <c r="C25" s="6">
+        <v>24</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="6">
-        <v>24</v>
-      </c>
-      <c r="E25" s="1">
-        <f>VLOOKUP(C25,Skill!C:E,3,FALSE)</f>
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="1">
+        <f>VLOOKUP(F26,Skill!C:E,3,FALSE)</f>
+        <v>77</v>
+      </c>
+      <c r="C26" s="6">
+        <v>25</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="6">
-        <v>25</v>
-      </c>
-      <c r="E26" s="1">
-        <f>VLOOKUP(C26,Skill!C:E,3,FALSE)</f>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="1">
+        <f>VLOOKUP(F27,Skill!C:E,3,FALSE)</f>
+        <v>75</v>
+      </c>
+      <c r="C27" s="6">
+        <v>26</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="F27" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="6">
-        <v>26</v>
-      </c>
-      <c r="E27" s="1">
-        <f>VLOOKUP(C27,Skill!C:E,3,FALSE)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="1">
+        <f>VLOOKUP(F28,Skill!C:E,3,FALSE)</f>
+        <v>78</v>
+      </c>
+      <c r="C28" s="6">
+        <v>27</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="F28" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="6">
-        <v>27</v>
-      </c>
-      <c r="E28" s="1">
-        <f>VLOOKUP(C28,Skill!C:E,3,FALSE)</f>
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="1">
+        <f>VLOOKUP(F29,Skill!C:E,3,FALSE)</f>
+        <v>80</v>
+      </c>
+      <c r="C29" s="6">
+        <v>28</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="6">
-        <v>28</v>
-      </c>
-      <c r="E29" s="1">
-        <f>VLOOKUP(C29,Skill!C:E,3,FALSE)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="1">
+        <f>VLOOKUP(F30,Skill!C:E,3,FALSE)</f>
+        <v>84</v>
+      </c>
+      <c r="C30" s="6">
+        <v>29</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="F30" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="6">
-        <v>29</v>
-      </c>
-      <c r="E30" s="1">
-        <f>VLOOKUP(C30,Skill!C:E,3,FALSE)</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="1">
+        <f>VLOOKUP(F31,Skill!C:E,3,FALSE)</f>
+        <v>81</v>
+      </c>
+      <c r="C31" s="6">
+        <v>30</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="F31" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="6">
-        <v>30</v>
-      </c>
-      <c r="E31" s="1">
-        <f>VLOOKUP(C31,Skill!C:E,3,FALSE)</f>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="1">
+        <f>VLOOKUP(F32,Skill!C:E,3,FALSE)</f>
+        <v>82</v>
+      </c>
+      <c r="C32" s="6">
+        <v>31</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="F32" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="6">
-        <v>31</v>
-      </c>
-      <c r="E32" s="1">
-        <f>VLOOKUP(C32,Skill!C:E,3,FALSE)</f>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="1">
+        <f>VLOOKUP(F33,Skill!C:E,3,FALSE)</f>
+        <v>83</v>
+      </c>
+      <c r="C33" s="6">
+        <v>32</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="F33" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="6">
-        <v>32</v>
-      </c>
-      <c r="E33" s="1">
-        <f>VLOOKUP(C33,Skill!C:E,3,FALSE)</f>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="1">
+        <f>VLOOKUP(F34,Skill!C:E,3,FALSE)</f>
+        <v>95</v>
+      </c>
+      <c r="C34" s="6">
+        <v>33</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="6">
-        <v>33</v>
-      </c>
-      <c r="E34" s="1">
-        <f>VLOOKUP(C34,Skill!C:E,3,FALSE)</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="1">
+        <f>VLOOKUP(F35,Skill!C:E,3,FALSE)</f>
+        <v>96</v>
+      </c>
+      <c r="C35" s="6">
+        <v>34</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="6">
-        <v>34</v>
-      </c>
-      <c r="E35" s="1">
-        <f>VLOOKUP(C35,Skill!C:E,3,FALSE)</f>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="1">
+        <f>VLOOKUP(F36,Skill!C:E,3,FALSE)</f>
+        <v>97</v>
+      </c>
+      <c r="C36" s="6">
+        <v>35</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="6">
-        <v>35</v>
-      </c>
-      <c r="E36" s="1">
-        <f>VLOOKUP(C36,Skill!C:E,3,FALSE)</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="1">
+        <f>VLOOKUP(F37,Skill!C:E,3,FALSE)</f>
+        <v>98</v>
+      </c>
+      <c r="C37" s="6">
+        <v>36</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="F37" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="6">
-        <v>36</v>
-      </c>
-      <c r="E37" s="1">
-        <f>VLOOKUP(C37,Skill!C:E,3,FALSE)</f>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="1">
+        <f>VLOOKUP(F38,Skill!C:E,3,FALSE)</f>
+        <v>99</v>
+      </c>
+      <c r="C38" s="6">
+        <v>37</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="F38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="6">
-        <v>37</v>
-      </c>
-      <c r="E38" s="1">
-        <f>VLOOKUP(C38,Skill!C:E,3,FALSE)</f>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="1">
+        <f>VLOOKUP(F39,Skill!C:E,3,FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="C39" s="6">
+        <v>38</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="F39" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="6">
-        <v>38</v>
-      </c>
-      <c r="E39" s="1">
-        <f>VLOOKUP(C39,Skill!C:E,3,FALSE)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="1">
+        <f>VLOOKUP(F40,Skill!C:E,3,FALSE)</f>
+        <v>101</v>
+      </c>
+      <c r="C40" s="6">
+        <v>39</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="F40" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="6">
-        <v>39</v>
-      </c>
-      <c r="E40" s="1">
-        <f>VLOOKUP(C40,Skill!C:E,3,FALSE)</f>
-        <v>101</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="1">
+        <f>VLOOKUP(F41,Skill!C:E,3,FALSE)</f>
+        <v>102</v>
+      </c>
+      <c r="C41" s="6">
+        <v>40</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="F41" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="6">
-        <v>40</v>
-      </c>
-      <c r="E41" s="1">
-        <f>VLOOKUP(C41,Skill!C:E,3,FALSE)</f>
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="1">
+        <f>VLOOKUP(F42,Skill!C:E,3,FALSE)</f>
+        <v>103</v>
+      </c>
+      <c r="C42" s="6">
+        <v>41</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="F42" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D42" s="6">
-        <v>41</v>
-      </c>
-      <c r="E42" s="1">
-        <f>VLOOKUP(C42,Skill!C:E,3,FALSE)</f>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="1">
+        <f>VLOOKUP(F43,Skill!C:E,3,FALSE)</f>
+        <v>104</v>
+      </c>
+      <c r="C43" s="6">
+        <v>42</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="F43" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D43" s="6">
-        <v>42</v>
-      </c>
-      <c r="E43" s="1">
-        <f>VLOOKUP(C43,Skill!C:E,3,FALSE)</f>
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="1">
+        <f>VLOOKUP(F44,Skill!C:E,3,FALSE)</f>
+        <v>105</v>
+      </c>
+      <c r="C44" s="6">
+        <v>43</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="F44" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="6">
-        <v>43</v>
-      </c>
-      <c r="E44" s="1">
-        <f>VLOOKUP(C44,Skill!C:E,3,FALSE)</f>
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="1">
+        <f>VLOOKUP(F45,Skill!C:E,3,FALSE)</f>
+        <v>106</v>
+      </c>
+      <c r="C45" s="6">
+        <v>44</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="F45" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D45" s="6">
-        <v>44</v>
-      </c>
-      <c r="E45" s="1">
-        <f>VLOOKUP(C45,Skill!C:E,3,FALSE)</f>
-        <v>106</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="1">
+        <f>VLOOKUP(F46,Skill!C:E,3,FALSE)</f>
+        <v>107</v>
+      </c>
+      <c r="C46" s="6">
+        <v>45</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="F46" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="6">
-        <v>45</v>
-      </c>
-      <c r="E46" s="1">
-        <f>VLOOKUP(C46,Skill!C:E,3,FALSE)</f>
-        <v>107</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="1">
+        <f>VLOOKUP(F47,Skill!C:E,3,FALSE)</f>
+        <v>108</v>
+      </c>
+      <c r="C47" s="6">
+        <v>46</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="F47" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D47" s="6">
-        <v>46</v>
-      </c>
-      <c r="E47" s="1">
-        <f>VLOOKUP(C47,Skill!C:E,3,FALSE)</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="1">
+        <f>VLOOKUP(F48,Skill!C:E,3,FALSE)</f>
+        <v>109</v>
+      </c>
+      <c r="C48" s="6">
+        <v>47</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="F48" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D48" s="6">
-        <v>47</v>
-      </c>
-      <c r="E48" s="1">
-        <f>VLOOKUP(C48,Skill!C:E,3,FALSE)</f>
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="1">
+        <f>VLOOKUP(F49,Skill!C:E,3,FALSE)</f>
+        <v>110</v>
+      </c>
+      <c r="C49" s="6">
+        <v>48</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="F49" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D49" s="6">
-        <v>48</v>
-      </c>
-      <c r="E49" s="1">
-        <f>VLOOKUP(C49,Skill!C:E,3,FALSE)</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="1">
+        <f>VLOOKUP(F50,Skill!C:E,3,FALSE)</f>
+        <v>111</v>
+      </c>
+      <c r="C50" s="6">
+        <v>49</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="F50" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D50" s="6">
-        <v>49</v>
-      </c>
-      <c r="E50" s="1">
-        <f>VLOOKUP(C50,Skill!C:E,3,FALSE)</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="1">
+        <f>VLOOKUP(F51,Skill!C:E,3,FALSE)</f>
+        <v>112</v>
+      </c>
+      <c r="C51" s="6">
+        <v>50</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="F51" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="6">
-        <v>50</v>
-      </c>
-      <c r="E51" s="1">
-        <f>VLOOKUP(C51,Skill!C:E,3,FALSE)</f>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="1">
+        <f>VLOOKUP(F52,Skill!C:E,3,FALSE)</f>
+        <v>114</v>
+      </c>
+      <c r="C52" s="6">
+        <v>51</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="F52" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="6">
-        <v>51</v>
-      </c>
-      <c r="E52" s="1">
-        <f>VLOOKUP(C52,Skill!C:E,3,FALSE)</f>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="1">
+        <f>VLOOKUP(F53,Skill!C:E,3,FALSE)</f>
+        <v>115</v>
+      </c>
+      <c r="C53" s="6">
+        <v>52</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="F53" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D53" s="6">
-        <v>52</v>
-      </c>
-      <c r="E53" s="1">
-        <f>VLOOKUP(C53,Skill!C:E,3,FALSE)</f>
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="1">
+        <f>VLOOKUP(F54,Skill!C:E,3,FALSE)</f>
+        <v>116</v>
+      </c>
+      <c r="C54" s="6">
+        <v>53</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="F54" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D54" s="6">
-        <v>53</v>
-      </c>
-      <c r="E54" s="1">
-        <f>VLOOKUP(C54,Skill!C:E,3,FALSE)</f>
-        <v>116</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="1">
+        <f>VLOOKUP(F55,Skill!C:E,3,FALSE)</f>
+        <v>117</v>
+      </c>
+      <c r="C55" s="6">
+        <v>54</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="F55" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D55" s="6">
-        <v>54</v>
-      </c>
-      <c r="E55" s="1">
-        <f>VLOOKUP(C55,Skill!C:E,3,FALSE)</f>
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="1">
+        <f>VLOOKUP(F56,Skill!C:E,3,FALSE)</f>
+        <v>125</v>
+      </c>
+      <c r="C56" s="6">
+        <v>55</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="F56" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D56" s="6">
-        <v>55</v>
-      </c>
-      <c r="E56" s="1">
-        <f>VLOOKUP(C56,Skill!C:E,3,FALSE)</f>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="1">
+        <f>VLOOKUP(F57,Skill!C:E,3,FALSE)</f>
+        <v>132</v>
+      </c>
+      <c r="C57" s="6">
+        <v>56</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="F57" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="6">
-        <v>56</v>
-      </c>
-      <c r="E57" s="1">
-        <f>VLOOKUP(C57,Skill!C:E,3,FALSE)</f>
-        <v>132</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="1">
+        <f>VLOOKUP(F58,Skill!C:E,3,FALSE)</f>
+        <v>135</v>
+      </c>
+      <c r="C58" s="6">
+        <v>57</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="F58" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D58" s="6">
-        <v>57</v>
-      </c>
-      <c r="E58" s="1">
-        <f>VLOOKUP(C58,Skill!C:E,3,FALSE)</f>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="1">
+        <f>VLOOKUP(F59,Skill!C:E,3,FALSE)</f>
+        <v>141</v>
+      </c>
+      <c r="C59" s="6">
+        <v>58</v>
+      </c>
+      <c r="E59" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="F59" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D59" s="6">
-        <v>58</v>
-      </c>
-      <c r="E59" s="1">
-        <f>VLOOKUP(C59,Skill!C:E,3,FALSE)</f>
-        <v>141</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="1">
+        <f>VLOOKUP(F60,Skill!C:E,3,FALSE)</f>
+        <v>142</v>
+      </c>
+      <c r="C60" s="6">
+        <v>59</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="F60" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D60" s="6">
-        <v>59</v>
-      </c>
-      <c r="E60" s="1">
-        <f>VLOOKUP(C60,Skill!C:E,3,FALSE)</f>
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="1">
+        <f>VLOOKUP(F61,Skill!C:E,3,FALSE)</f>
+        <v>146</v>
+      </c>
+      <c r="C61" s="6">
+        <v>60</v>
+      </c>
+      <c r="E61" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="F61" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D61" s="6">
-        <v>60</v>
-      </c>
-      <c r="E61" s="1">
-        <f>VLOOKUP(C61,Skill!C:E,3,FALSE)</f>
-        <v>146</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="1">
+        <f>VLOOKUP(F62,Skill!C:E,3,FALSE)</f>
+        <v>147</v>
+      </c>
+      <c r="C62" s="6">
+        <v>61</v>
+      </c>
+      <c r="E62" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="F62" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D62" s="6">
-        <v>61</v>
-      </c>
-      <c r="E62" s="1">
-        <f>VLOOKUP(C62,Skill!C:E,3,FALSE)</f>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="1">
+        <f>VLOOKUP(F63,Skill!C:E,3,FALSE)</f>
+        <v>148</v>
+      </c>
+      <c r="C63" s="6">
+        <v>62</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="F63" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D63" s="6">
-        <v>62</v>
-      </c>
-      <c r="E63" s="1">
-        <f>VLOOKUP(C63,Skill!C:E,3,FALSE)</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="1">
+        <f>VLOOKUP(F64,Skill!C:E,3,FALSE)</f>
+        <v>156</v>
+      </c>
+      <c r="C64" s="6">
+        <v>63</v>
+      </c>
+      <c r="E64" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="F64" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D64" s="6">
-        <v>63</v>
-      </c>
-      <c r="E64" s="1">
-        <f>VLOOKUP(C64,Skill!C:E,3,FALSE)</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="1">
+        <f>VLOOKUP(F65,Skill!C:E,3,FALSE)</f>
+        <v>158</v>
+      </c>
+      <c r="C65" s="6">
+        <v>64</v>
+      </c>
+      <c r="E65" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="F65" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D65" s="6">
-        <v>64</v>
-      </c>
-      <c r="E65" s="1">
-        <f>VLOOKUP(C65,Skill!C:E,3,FALSE)</f>
-        <v>158</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="1">
+        <f>VLOOKUP(F66,Skill!C:E,3,FALSE)</f>
+        <v>157</v>
+      </c>
+      <c r="C66" s="6">
+        <v>65</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="F66" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D66" s="6">
-        <v>65</v>
-      </c>
-      <c r="E66" s="1">
-        <f>VLOOKUP(C66,Skill!C:E,3,FALSE)</f>
-        <v>157</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="1">
+        <f>VLOOKUP(F67,Skill!C:E,3,FALSE)</f>
+        <v>160</v>
+      </c>
+      <c r="C67" s="6">
+        <v>66</v>
+      </c>
+      <c r="E67" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="F67" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D67" s="6">
-        <v>66</v>
-      </c>
-      <c r="E67" s="1">
-        <f>VLOOKUP(C67,Skill!C:E,3,FALSE)</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="1">
+        <f>VLOOKUP(F68,Skill!C:E,3,FALSE)</f>
+        <v>161</v>
+      </c>
+      <c r="C68" s="6">
+        <v>67</v>
+      </c>
+      <c r="E68" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="F68" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D68" s="6">
-        <v>67</v>
-      </c>
-      <c r="E68" s="1">
-        <f>VLOOKUP(C68,Skill!C:E,3,FALSE)</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="1">
+        <f>VLOOKUP(F69,Skill!C:E,3,FALSE)</f>
+        <v>162</v>
+      </c>
+      <c r="C69" s="6">
+        <v>68</v>
+      </c>
+      <c r="E69" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="F69" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D69" s="6">
-        <v>68</v>
-      </c>
-      <c r="E69" s="1">
-        <f>VLOOKUP(C69,Skill!C:E,3,FALSE)</f>
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="1">
+        <f>VLOOKUP(F70,Skill!C:E,3,FALSE)</f>
+        <v>165</v>
+      </c>
+      <c r="C70" s="6">
+        <v>69</v>
+      </c>
+      <c r="E70" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="F70" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D70" s="6">
-        <v>69</v>
-      </c>
-      <c r="E70" s="1">
-        <f>VLOOKUP(C70,Skill!C:E,3,FALSE)</f>
-        <v>165</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>70</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="1">
+        <f>VLOOKUP(F71,Skill!C:E,3,FALSE)</f>
+        <v>167</v>
+      </c>
+      <c r="C71" s="6">
+        <v>70</v>
+      </c>
+      <c r="E71" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="F71" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D71" s="6">
-        <v>70</v>
-      </c>
-      <c r="E71" s="1">
-        <f>VLOOKUP(C71,Skill!C:E,3,FALSE)</f>
-        <v>167</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="1">
+        <f>VLOOKUP(F72,Skill!C:E,3,FALSE)</f>
+        <v>168</v>
+      </c>
+      <c r="C72" s="6">
+        <v>71</v>
+      </c>
+      <c r="E72" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="F72" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D72" s="6">
-        <v>71</v>
-      </c>
-      <c r="E72" s="1">
-        <f>VLOOKUP(C72,Skill!C:E,3,FALSE)</f>
-        <v>168</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="1">
+        <f>VLOOKUP(F73,Skill!C:E,3,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="C73" s="6">
+        <v>72</v>
+      </c>
+      <c r="E73" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="F73" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D73" s="6">
-        <v>72</v>
-      </c>
-      <c r="E73" s="1">
-        <f>VLOOKUP(C73,Skill!C:E,3,FALSE)</f>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>73</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="1">
+        <f>VLOOKUP(F74,Skill!C:E,3,FALSE)</f>
+        <v>173</v>
+      </c>
+      <c r="C74" s="6">
+        <v>73</v>
+      </c>
+      <c r="E74" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="F74" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D74" s="6">
-        <v>73</v>
-      </c>
-      <c r="E74" s="1">
-        <f>VLOOKUP(C74,Skill!C:E,3,FALSE)</f>
-        <v>173</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="1">
+        <f>VLOOKUP(F75,Skill!C:E,3,FALSE)</f>
+        <v>195</v>
+      </c>
+      <c r="C75" s="6">
+        <v>74</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="F75" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D75" s="6">
-        <v>74</v>
-      </c>
-      <c r="E75" s="1">
-        <f>VLOOKUP(C75,Skill!C:E,3,FALSE)</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>75</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="1">
+        <f>VLOOKUP(F76,Skill!C:E,3,FALSE)</f>
+        <v>204</v>
+      </c>
+      <c r="C76" s="6">
+        <v>75</v>
+      </c>
+      <c r="E76" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="F76" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D76" s="6">
-        <v>75</v>
-      </c>
-      <c r="E76" s="1">
-        <f>VLOOKUP(C76,Skill!C:E,3,FALSE)</f>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>76</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="1">
+        <f>VLOOKUP(F77,Skill!C:E,3,FALSE)</f>
+        <v>193</v>
+      </c>
+      <c r="C77" s="6">
+        <v>76</v>
+      </c>
+      <c r="E77" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="F77" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="6">
-        <v>76</v>
-      </c>
-      <c r="E77" s="1">
-        <f>VLOOKUP(C77,Skill!C:E,3,FALSE)</f>
-        <v>193</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>77</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="1">
+        <f>VLOOKUP(F78,Skill!C:E,3,FALSE)</f>
+        <v>216</v>
+      </c>
+      <c r="C78" s="6">
+        <v>77</v>
+      </c>
+      <c r="E78" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="F78" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="6">
-        <v>77</v>
-      </c>
-      <c r="E78" s="1">
-        <f>VLOOKUP(C78,Skill!C:E,3,FALSE)</f>
-        <v>216</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="1">
+        <f>VLOOKUP(F79,Skill!C:E,3,FALSE)</f>
+        <v>217</v>
+      </c>
+      <c r="C79" s="6">
+        <v>78</v>
+      </c>
+      <c r="E79" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="F79" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="6">
-        <v>78</v>
-      </c>
-      <c r="E79" s="1">
-        <f>VLOOKUP(C79,Skill!C:E,3,FALSE)</f>
-        <v>217</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="1">
+        <f>VLOOKUP(F80,Skill!C:E,3,FALSE)</f>
+        <v>218</v>
+      </c>
+      <c r="C80" s="6">
+        <v>79</v>
+      </c>
+      <c r="E80" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="F80" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="D80" s="6">
-        <v>79</v>
-      </c>
-      <c r="E80" s="1">
-        <f>VLOOKUP(C80,Skill!C:E,3,FALSE)</f>
-        <v>218</v>
       </c>
     </row>
   </sheetData>
